--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="123">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Exposure Information</t>
+    <t>Logical model - FR LM Exposure Information</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,17 +375,17 @@
     <t>fr-lm-section.entry</t>
   </si>
   <si>
-    <t>fr-lm-exposure-information.entry.quantiteExposition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-quantite-exposition
+    <t>fr-lm-exposure-information.subSection.quantityExposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-quantity-exposure
 </t>
   </si>
   <si>
     <t>Entrée Quantité</t>
   </si>
   <si>
-    <t>fr-lm-exposure-information.entry.administrationRadiopharmaceutique</t>
+    <t>fr-lm-exposure-information.subSection.radiopharmaceuticalAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-administration
@@ -393,22 +393,6 @@
   </si>
   <si>
     <t>Entrée administration des produits radiopharmaceutiques</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.entry.observationGrossesse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation
-</t>
-  </si>
-  <si>
-    <t>Entrée observation de grossesse</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.entry.observationIndication</t>
-  </si>
-  <si>
-    <t>Entrée observation indication</t>
   </si>
 </sst>
 </file>
@@ -710,11 +694,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.57421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.57421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -744,7 +728,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="56.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="59.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2160,206 +2144,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
